--- a/reports/history/build-6/Failed_Test_Cases.xlsx
+++ b/reports/history/build-6/Failed_Test_Cases.xlsx
@@ -22,61 +22,61 @@
     <t>Test Name</t>
   </si>
   <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Execution Time (ms)</t>
+  </si>
+  <si>
     <t>Priority</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Execution Time (ms)</t>
-  </si>
-  <si>
     <t>Failure Reason</t>
   </si>
   <si>
-    <t>TC_AUTH_010</t>
+    <t>TC_WEB_AUTH_010</t>
   </si>
   <si>
     <t>Authentication</t>
   </si>
   <si>
-    <t>Authentication - Functional Validation Scenario 10</t>
+    <t>Authentication - Live E2E Scenario 10</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
   <si>
     <t>P1</t>
   </si>
   <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>OTP validation mismatch</t>
-  </si>
-  <si>
-    <t>TC_FORM_008</t>
+    <t>Invalid OTP validation message mismatch on live UI</t>
+  </si>
+  <si>
+    <t>TC_WEB_FORM_008</t>
   </si>
   <si>
     <t>Forms</t>
   </si>
   <si>
-    <t>Forms - Functional Validation Scenario 8</t>
-  </si>
-  <si>
-    <t>Validation message missing</t>
-  </si>
-  <si>
-    <t>TC_FILE_002</t>
+    <t>Forms - Live E2E Scenario 8</t>
+  </si>
+  <si>
+    <t>Mandatory field highlight color validation failure</t>
+  </si>
+  <si>
+    <t>TC_WEB_FILE_002</t>
   </si>
   <si>
     <t>File Upload</t>
   </si>
   <si>
-    <t>File Upload - Functional Validation Scenario 2</t>
+    <t>File Upload - Live E2E Scenario 2</t>
   </si>
   <si>
     <t>P0</t>
   </si>
   <si>
-    <t>Application crash on large payload upload</t>
+    <t>Large file upload progress bar timeout on live deployment</t>
   </si>
 </sst>
 </file>
@@ -471,8 +471,9 @@
     <col min="1" max="1" width="18" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="40" customWidth="1"/>
-    <col min="4" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="20" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="45" customWidth="1"/>
   </cols>
   <sheetData>
@@ -512,11 +513,11 @@
       <c r="D2" t="s">
         <v>10</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2">
+        <v>261</v>
+      </c>
+      <c r="F2" t="s">
         <v>11</v>
-      </c>
-      <c r="F2">
-        <v>475</v>
       </c>
       <c r="G2" t="s">
         <v>12</v>
@@ -535,11 +536,11 @@
       <c r="D3" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3">
+        <v>248</v>
+      </c>
+      <c r="F3" t="s">
         <v>11</v>
-      </c>
-      <c r="F3">
-        <v>333</v>
       </c>
       <c r="G3" t="s">
         <v>16</v>
@@ -556,13 +557,13 @@
         <v>19</v>
       </c>
       <c r="D4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>245</v>
+      </c>
+      <c r="F4" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>11</v>
-      </c>
-      <c r="F4">
-        <v>333</v>
       </c>
       <c r="G4" t="s">
         <v>21</v>
